--- a/0 Model Price Targets 0.xlsx
+++ b/0 Model Price Targets 0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F8E2AC-1457-4ABA-AE79-1111B85E5F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D452F2EB-FD77-4068-96AF-A5D3CF40A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="2400" windowWidth="21600" windowHeight="13185" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="481">
   <si>
     <t>Date</t>
   </si>
@@ -1351,9 +1351,6 @@
     <t>CRDO</t>
   </si>
   <si>
-    <t>C.E.s = 50% TLT, 50% GLD … DXY has been getting punished … anything but</t>
-  </si>
-  <si>
     <t>dug into the financials and market a bit more + some reporting from Karlina … going to hold a tiny position just because I think $160.00 is a decent price, but I only see headwinds ahead</t>
   </si>
   <si>
@@ -1474,6 +1471,30 @@
   </si>
   <si>
     <t>NFLX</t>
+  </si>
+  <si>
+    <t>bet that M&amp;A window is back open with new admin and booting of Lina Khan … lower antitrust scrutiny</t>
+  </si>
+  <si>
+    <t>Bet on rare disease portfolio</t>
+  </si>
+  <si>
+    <t>This small bottling segment has had two incredible run-ups in share price as share buyback program continues on … very small public float / daily trading volume</t>
+  </si>
+  <si>
+    <t>Cut large portion of my position after oracle deal was announced … sold oracle after deal was announced and crazy earnings projections … ORCL has since returned to a 'fair value' and the firms bond market is signaling potentional financial distress being priced in over the next 10 years ... probability of default currently stands at ~7%</t>
+  </si>
+  <si>
+    <t>C.E.s = 50% TLT, 50% GLD … DXY has been getting punished and I think the dollar devaluation campaign will be continued by Bessent and the current financial regime … anything but USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing position and entering into basket of smaller prop research companies … BMRN is misunderstood by the market, but the companies management team continues to throw-out promising and innovative drugs because the potential TAM is too small </t>
+  </si>
+  <si>
+    <t>I like paypal … opportunity to build on my position</t>
+  </si>
+  <si>
+    <t>CAPR</t>
   </si>
 </sst>
 </file>
@@ -4088,7 +4109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J163"/>
+  <dimension ref="B2:J167"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="13" customWidth="1"/>
@@ -4392,7 +4413,7 @@
         <v>1.0887728459530028</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>21</v>
@@ -4417,7 +4438,7 @@
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
       <c r="I12" s="18" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>20</v>
@@ -4442,7 +4463,7 @@
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
       <c r="I13" s="18" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>20</v>
@@ -4450,7 +4471,7 @@
     </row>
     <row r="14" spans="2:10" ht="14.25" customHeight="1">
       <c r="B14" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C14" s="14">
         <v>45695</v>
@@ -4510,7 +4531,7 @@
     </row>
     <row r="16" spans="2:10" ht="14.25" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C16" s="14">
         <v>45706</v>
@@ -4842,7 +4863,7 @@
         <v>0.2721722909954214</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>109</v>
+        <v>479</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>21</v>
@@ -5107,7 +5128,7 @@
       <c r="G36" s="16"/>
       <c r="H36" s="17"/>
       <c r="I36" s="18" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="J36" s="15" t="s">
         <v>20</v>
@@ -5137,7 +5158,7 @@
         <v>1.990871127512861E-2</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J37" s="15" t="s">
         <v>21</v>
@@ -5188,7 +5209,7 @@
         <v>0.12928722653493296</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J39" s="15" t="s">
         <v>21</v>
@@ -5303,7 +5324,7 @@
         <v>-0.57823129251700678</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J43" s="15" t="s">
         <v>21</v>
@@ -5333,7 +5354,7 @@
         <v>1.2028038186978587</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J44" s="15" t="s">
         <v>21</v>
@@ -5572,6 +5593,12 @@
         <f t="shared" si="5"/>
         <v>0.10051159246761721</v>
       </c>
+      <c r="I52" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="53" spans="2:10" ht="14.25" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5630,7 +5657,7 @@
         <v>371</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="14.25" customHeight="1">
@@ -5838,9 +5865,19 @@
       <c r="F62" s="15">
         <v>4</v>
       </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="15"/>
+      <c r="G62" s="13">
+        <v>164.75</v>
+      </c>
+      <c r="H62" s="17">
+        <f>G62/E62-1</f>
+        <v>0.54130414444756281</v>
+      </c>
+      <c r="I62" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="63" spans="2:10" ht="14.25" customHeight="1">
       <c r="B63" s="13" t="s">
@@ -5955,7 +5992,12 @@
         <f t="shared" si="7"/>
         <v>-9.1703056768558944E-2</v>
       </c>
-      <c r="I66" s="18"/>
+      <c r="I66" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="67" spans="2:10" ht="14.25" customHeight="1">
       <c r="B67" s="13" t="s">
@@ -6139,7 +6181,7 @@
         <v>0.36585365853658547</v>
       </c>
       <c r="I73" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J73" s="15" t="s">
         <v>21</v>
@@ -6161,6 +6203,13 @@
       <c r="F74" s="15">
         <v>4</v>
       </c>
+      <c r="G74" s="16">
+        <v>187.5</v>
+      </c>
+      <c r="H74" s="17">
+        <f>G74/E74-1</f>
+        <v>7.7586206896551824E-2</v>
+      </c>
       <c r="I74" s="18" t="s">
         <v>374</v>
       </c>
@@ -6192,7 +6241,7 @@
         <v>0.2558139534883721</v>
       </c>
       <c r="I75" s="18" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J75" s="15" t="s">
         <v>21</v>
@@ -6400,6 +6449,13 @@
       <c r="F85" s="15">
         <v>5</v>
       </c>
+      <c r="G85" s="16">
+        <v>188.5</v>
+      </c>
+      <c r="H85" s="17">
+        <f>G85/E85-1</f>
+        <v>6.3709722927600021E-2</v>
+      </c>
       <c r="I85" s="18" t="s">
         <v>109</v>
       </c>
@@ -6547,7 +6603,7 @@
         <v>0.21111111111111103</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J91" s="15" t="s">
         <v>21</v>
@@ -6577,7 +6633,7 @@
         <v>8.7499999999999911E-2</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J92" s="15" t="s">
         <v>21</v>
@@ -6789,7 +6845,7 @@
         <v>3</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J100" s="15" t="s">
         <v>20</v>
@@ -6842,7 +6898,7 @@
         <v>-0.17333333333333334</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>21</v>
@@ -6862,7 +6918,7 @@
         <v>135</v>
       </c>
       <c r="F103" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I103" s="18"/>
     </row>
@@ -6900,11 +6956,18 @@
       <c r="F105" s="15">
         <v>4</v>
       </c>
+      <c r="G105" s="16">
+        <v>54</v>
+      </c>
+      <c r="H105" s="17">
+        <f>G105/E105-1</f>
+        <v>-3.5714285714285698E-2</v>
+      </c>
       <c r="I105" s="18" t="s">
-        <v>109</v>
+        <v>478</v>
       </c>
       <c r="J105" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="2:10" ht="14.25" customHeight="1">
@@ -7017,7 +7080,7 @@
         <v>175</v>
       </c>
       <c r="F111" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I111" s="18"/>
     </row>
@@ -7038,7 +7101,7 @@
         <v>3</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J112" s="15" t="s">
         <v>20</v>
@@ -7086,7 +7149,7 @@
     </row>
     <row r="115" spans="2:10" ht="14.25" customHeight="1">
       <c r="B115" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C115" s="14">
         <v>45947</v>
@@ -7134,7 +7197,7 @@
     </row>
     <row r="117" spans="2:10" ht="14.25" customHeight="1">
       <c r="B117" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C117" s="14">
         <v>45952</v>
@@ -7156,7 +7219,7 @@
         <v>0.69090909090909092</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J117" s="15" t="s">
         <v>21</v>
@@ -7182,7 +7245,7 @@
     </row>
     <row r="119" spans="2:10" ht="14.25" customHeight="1">
       <c r="B119" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C119" s="14">
         <v>45954</v>
@@ -7220,7 +7283,7 @@
     </row>
     <row r="121" spans="2:10" ht="14.25" customHeight="1">
       <c r="B121" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C121" s="14">
         <v>45958</v>
@@ -7269,7 +7332,7 @@
         <v>5</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J123" s="15" t="s">
         <v>20</v>
@@ -7439,7 +7502,7 @@
         <v>45966</v>
       </c>
       <c r="D132" s="20" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E132" s="13">
         <v>127.25</v>
@@ -7455,7 +7518,7 @@
         <v>-0.14656188605108056</v>
       </c>
       <c r="I132" s="19" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J132" s="15" t="s">
         <v>21</v>
@@ -7469,7 +7532,7 @@
         <v>45966</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E133" s="16">
         <v>140</v>
@@ -7478,7 +7541,7 @@
         <v>5</v>
       </c>
       <c r="I133" s="18" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J133" s="15" t="s">
         <v>21</v>
@@ -7501,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="I134" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J134" s="15" t="s">
         <v>20</v>
@@ -7531,7 +7594,7 @@
         <v>0.22667130919220047</v>
       </c>
       <c r="I135" s="18" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J135" s="15" t="s">
         <v>21</v>
@@ -7539,7 +7602,7 @@
     </row>
     <row r="136" spans="2:10" ht="14.25" customHeight="1">
       <c r="B136" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C136" s="14">
         <v>45973</v>
@@ -7561,7 +7624,7 @@
         <v>0.19462875197472351</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J136" s="15" t="s">
         <v>21</v>
@@ -7591,7 +7654,7 @@
         <v>0.1155677655677656</v>
       </c>
       <c r="I137" s="18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J137" s="15" t="s">
         <v>21</v>
@@ -7599,7 +7662,7 @@
     </row>
     <row r="138" spans="2:10" ht="14.25" customHeight="1">
       <c r="B138" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C138" s="14">
         <v>45974</v>
@@ -7677,7 +7740,7 @@
         <v>45980</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E142" s="13">
         <v>194.55</v>
@@ -7693,7 +7756,7 @@
         <v>-8.6096119249550185E-2</v>
       </c>
       <c r="I142" s="18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J142" s="15" t="s">
         <v>21</v>
@@ -7768,7 +7831,7 @@
         <v>5</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J146" s="15" t="s">
         <v>21</v>
@@ -7791,7 +7854,7 @@
         <v>3</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J147" s="15" t="s">
         <v>21</v>
@@ -7799,7 +7862,7 @@
     </row>
     <row r="148" spans="2:10" ht="14.25" customHeight="1">
       <c r="B148" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C148" s="14">
         <v>45992</v>
@@ -7816,7 +7879,7 @@
     </row>
     <row r="149" spans="2:10" ht="14.25" customHeight="1">
       <c r="B149" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C149" s="14">
         <v>45994</v>
@@ -7833,13 +7896,13 @@
     </row>
     <row r="150" spans="2:10" ht="14.25" customHeight="1">
       <c r="B150" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C150" s="14">
         <v>45996</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E150" s="13">
         <v>70.58</v>
@@ -7850,7 +7913,7 @@
     </row>
     <row r="151" spans="2:10" ht="14.25" customHeight="1">
       <c r="B151" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C151" s="14">
         <v>45997</v>
@@ -7901,19 +7964,19 @@
     </row>
     <row r="154" spans="2:10" ht="14.25" customHeight="1">
       <c r="B154" s="13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C154" s="14">
         <v>46013</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>9</v>
+        <v>408</v>
       </c>
       <c r="E154" s="13">
         <v>396.92</v>
       </c>
       <c r="F154" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="2:10" ht="14.25" customHeight="1">
@@ -7930,12 +7993,12 @@
         <v>150.71</v>
       </c>
       <c r="F155" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="2:10" ht="14.25" customHeight="1">
       <c r="B156" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C156" s="14">
         <v>46016</v>
@@ -7952,7 +8015,7 @@
     </row>
     <row r="157" spans="2:10" ht="14.25" customHeight="1">
       <c r="B157" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C157" s="14">
         <v>46020</v>
@@ -8020,7 +8083,7 @@
     </row>
     <row r="161" spans="2:6" ht="14.25" customHeight="1">
       <c r="B161" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C161" s="14">
         <v>46030</v>
@@ -8037,24 +8100,24 @@
     </row>
     <row r="162" spans="2:6" ht="14.25" customHeight="1">
       <c r="B162" s="13" t="s">
-        <v>472</v>
+        <v>380</v>
       </c>
       <c r="C162" s="14">
-        <v>46031</v>
+        <v>45973</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>9</v>
       </c>
       <c r="E162" s="16">
-        <v>60.15</v>
+        <v>111.44</v>
       </c>
       <c r="F162" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="2:6" ht="14.25" customHeight="1">
       <c r="B163" s="13" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C163" s="14">
         <v>46031</v>
@@ -8062,10 +8125,78 @@
       <c r="D163" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E163" s="13">
+      <c r="E163" s="16">
+        <v>60.15</v>
+      </c>
+      <c r="F163" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6" ht="14.25" customHeight="1">
+      <c r="B164" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C164" s="14">
+        <v>46031</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="13">
         <v>90.73</v>
       </c>
-      <c r="F163" s="15">
+      <c r="F164" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6" ht="14.25" customHeight="1">
+      <c r="B165" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C165" s="14">
+        <v>46031</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E165" s="13">
+        <v>80.23</v>
+      </c>
+      <c r="F165" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6" ht="14.25" customHeight="1">
+      <c r="B166" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="C166" s="14">
+        <v>46031</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E166" s="13">
+        <v>23.92</v>
+      </c>
+      <c r="F166" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6" ht="14.25" customHeight="1">
+      <c r="B167" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C167" s="14">
+        <v>45667</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E167" s="13">
+        <v>587.88</v>
+      </c>
+      <c r="F167" s="15">
         <v>4</v>
       </c>
     </row>
